--- a/output/pdf_financials_xlsx/MCC.xlsx
+++ b/output/pdf_financials_xlsx/MCC.xlsx
@@ -1564,13 +1564,13 @@
         <v>0.373265</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.890117</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.177194</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.799969</v>
       </c>
     </row>
     <row r="35">
@@ -1626,13 +1626,13 @@
         <v>0.403265</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.920117</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.207194</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.829969</v>
       </c>
     </row>
     <row r="37">
@@ -1998,13 +1998,13 @@
         <v>0.016609</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.966844</v>
+        <v>0.076727</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.222505</v>
+        <v>0.045311</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.833743</v>
+        <v>0.033774</v>
       </c>
     </row>
     <row r="49">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/output/pdf_financials_xlsx/MCC.xlsx
+++ b/output/pdf_financials_xlsx/MCC.xlsx
@@ -1354,25 +1354,25 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.001324</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.001803</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.001798</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.00233</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.002374</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.001047</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.017496</v>
       </c>
     </row>
     <row r="29">
@@ -1387,25 +1387,25 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.146566</v>
+        <v>-2.145242</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.591352</v>
+        <v>-0.589549</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.370839</v>
+        <v>-1.369041</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.416114</v>
+        <v>-1.413784</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.013728</v>
+        <v>-1.011354</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.978504</v>
+        <v>-0.977457</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.058518</v>
+        <v>-3.041022</v>
       </c>
     </row>
     <row r="30">
@@ -3614,25 +3614,25 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.001324</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.001803</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.001798</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.00233</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.002374</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.001047</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.017496</v>
       </c>
     </row>
     <row r="101">
@@ -8400,7 +8400,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -8456,7 +8460,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -11870,7 +11878,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -11914,7 +11926,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MCC.xlsx
+++ b/output/pdf_financials_xlsx/MCC.xlsx
@@ -639,25 +639,25 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.155606</v>
+        <v>0.212202</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.160208</v>
+        <v>0.199707</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.161092</v>
+        <v>0.211649</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.205009</v>
+        <v>0.269427</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.18426</v>
+        <v>0.2406</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.181865</v>
+        <v>0.243699</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.203559</v>
+        <v>0.273185</v>
       </c>
     </row>
     <row r="8">
@@ -741,16 +741,16 @@
         <v>4.182783</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.205009</v>
+        <v>0.269427</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.18426</v>
+        <v>0.2406</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.181865</v>
+        <v>0.243699</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.203559</v>
+        <v>0.273185</v>
       </c>
     </row>
     <row r="11">
@@ -967,16 +967,16 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.103387</v>
+        <v>-0.103387</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.114947</v>
+        <v>-0.114947</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.08223</v>
+        <v>-0.08223</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.117455</v>
+        <v>-0.117455</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -3977,7 +3977,7 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001717</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -4759,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001717</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.5648919999999999</v>
+        <v>-0.573892</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.40871</v>
@@ -4792,7 +4792,7 @@
         <v>-0.928797</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.155066</v>
+        <v>-1.156783</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.638076</v>
@@ -10376,7 +10376,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -10430,7 +10434,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -11684,7 +11692,11 @@
           <t>Supplies and office expenses</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -14388,7 +14400,11 @@
           <t>Income tax recovery 16</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -15934,7 +15950,11 @@
           <t>Income tax recovery 18</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -16808,7 +16828,11 @@
           <t>Income tax recovery 15</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
